--- a/data/trans_camb/P1404-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1404-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -682,42 +682,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,38</t>
+          <t>-1,35; 0,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; -0,19</t>
+          <t>-1,83; -0,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,09</t>
+          <t>-0,72; 0,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,49</t>
+          <t>-0,9; 0,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 4,18</t>
+          <t>-0,22; 3,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,14</t>
+          <t>-0,94; 0,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,16</t>
+          <t>-0,95; 0,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,32</t>
+          <t>-0,57; 1,25</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>299,74%</t>
+          <t>275,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 144,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 135,28</t>
+          <t>-100,0; 171,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 447,37</t>
+          <t>-100,0; 448,55</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,49</t>
+          <t>0,46; 3,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,11</t>
+          <t>0,27; 3,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,27</t>
+          <t>-0,53; 2,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,98</t>
+          <t>-1,84; 1,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,22</t>
+          <t>-1,6; 1,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,25</t>
+          <t>-1,28; 2,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,7</t>
+          <t>-0,28; 1,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,76</t>
+          <t>-0,24; 1,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,89</t>
+          <t>-0,36; 1,74</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>46,63%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,69; 1338,45</t>
+          <t>24,23; 1370,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 1330,81</t>
+          <t>-12,27; 1030,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,7; 798,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-77,14; 113,1</t>
+          <t>-75,32; 116,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,69; 128,09</t>
+          <t>-64,96; 106,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,37; 209,89</t>
+          <t>-54,94; 197,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,16; 220,22</t>
+          <t>-21,41; 230,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 227,93</t>
+          <t>-17,61; 226,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 254,45</t>
+          <t>-29,45; 218,87</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>-1,82</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-0,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,89</t>
+          <t>-1,03; 4,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,44</t>
+          <t>-2,06; 2,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 3,05</t>
+          <t>-1,52; 3,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,3</t>
+          <t>-1,72; 2,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,96</t>
+          <t>-2,98; 0,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,87</t>
+          <t>-3,62; -0,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,48</t>
+          <t>-0,65; 2,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,19</t>
+          <t>-1,89; 1,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 0,69</t>
+          <t>-2,07; 0,95</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-65,07%</t>
+          <t>-49,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-21,84%</t>
+          <t>-13,5%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 123,8</t>
+          <t>-19,88; 125,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 76,55</t>
+          <t>-38,01; 79,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,66; 86,23</t>
+          <t>-29,93; 95,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,84; 96,7</t>
+          <t>-38,1; 95,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,52; 43,09</t>
+          <t>-62,1; 29,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,82; -27,75</t>
+          <t>-73,1; 1,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 78,34</t>
+          <t>-14,73; 80,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,87; 35,94</t>
+          <t>-38,94; 35,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,53; 23,16</t>
+          <t>-44,13; 31,11</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>3,49</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>1,81</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>2,6</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 2,36</t>
+          <t>-4,86; 2,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 3,27</t>
+          <t>-3,84; 3,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 4,81</t>
+          <t>-0,59; 7,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 7,98</t>
+          <t>0,7; 8,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 6,12</t>
+          <t>-1,08; 5,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 5,44</t>
+          <t>-1,53; 4,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 4,15</t>
+          <t>-0,97; 4,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,59</t>
+          <t>-1,57; 3,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 3,65</t>
+          <t>0,02; 4,91</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-4,69%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 29,11</t>
+          <t>-39,72; 34,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 41,58</t>
+          <t>-32,28; 38,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,91; 52,18</t>
+          <t>-7,6; 85,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,0; 126,24</t>
+          <t>5,89; 127,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 95,28</t>
+          <t>-11,35; 81,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 88,32</t>
+          <t>-14,65; 70,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 52,02</t>
+          <t>-9,96; 57,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 45,96</t>
+          <t>-14,77; 44,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,45; 43,17</t>
+          <t>0,59; 64,4</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,06</t>
+          <t>5,28</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>3,82</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>4,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 7,51</t>
+          <t>-4,16; 7,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 7,54</t>
+          <t>-3,29; 7,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,07; 11,0</t>
+          <t>0,07; 9,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 10,51</t>
+          <t>-1,08; 11,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 8,97</t>
+          <t>-3,18; 8,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 8,56</t>
+          <t>-1,62; 8,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 7,08</t>
+          <t>-0,83; 7,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 6,52</t>
+          <t>-1,53; 6,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 8,39</t>
+          <t>0,63; 7,97</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,53; 51,12</t>
+          <t>-20,15; 49,59</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 52,01</t>
+          <t>-16,3; 50,73</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5,64; 78,3</t>
+          <t>0,2; 67,56</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 58,73</t>
+          <t>-4,61; 62,99</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 48,45</t>
+          <t>-13,27; 47,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 48,1</t>
+          <t>-6,17; 48,61</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 39,89</t>
+          <t>-4,49; 41,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 37,51</t>
+          <t>-6,82; 38,01</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5,77; 48,22</t>
+          <t>2,61; 45,09</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10,65</t>
+          <t>10,32</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,01</t>
+          <t>7,24</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22,83</t>
+          <t>8,55</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>9,55; 24,01</t>
+          <t>9,63; 24,92</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,57; 18,54</t>
+          <t>5,23; 18,98</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5,15; 16,61</t>
+          <t>4,83; 16,3</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 13,04</t>
+          <t>-0,57; 13,64</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 9,73</t>
+          <t>-4,27; 9,32</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,21; 56,07</t>
+          <t>1,76; 12,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,18; 17,1</t>
+          <t>5,89; 15,97</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,76</t>
+          <t>2,46; 11,47</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7,39; 49,26</t>
+          <t>4,48; 12,5</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>103,35%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>41,22; 147,32</t>
+          <t>41,63; 155,39</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20,5; 112,5</t>
+          <t>22,09; 117,66</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21,88; 104,13</t>
+          <t>19,99; 102,59</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0,13; 52,41</t>
+          <t>-1,79; 55,26</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 38,54</t>
+          <t>-14,03; 37,28</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,52; 221,61</t>
+          <t>5,51; 50,9</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,01; 77,18</t>
+          <t>22,4; 71,96</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7,68; 54,27</t>
+          <t>8,9; 51,89</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>29,67; 223,97</t>
+          <t>16,73; 57,62</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15,18</t>
+          <t>15,25</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,31</t>
+          <t>15,85</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>15,8</t>
+          <t>15,54</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,18; 20,15</t>
+          <t>3,06; 19,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,59; 17,81</t>
+          <t>2,13; 17,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8,35; 22,66</t>
+          <t>8,03; 22,17</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,75; 16,66</t>
+          <t>0,9; 15,9</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,42; 15,4</t>
+          <t>0,6; 15,29</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,08; 22,13</t>
+          <t>9,38; 21,51</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,28; 16,26</t>
+          <t>4,46; 15,57</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,76; 14,4</t>
+          <t>3,06; 14,25</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11,46; 20,36</t>
+          <t>10,96; 20,33</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>64,8%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12,22; 116,5</t>
+          <t>11,84; 114,35</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10,44; 112,79</t>
+          <t>6,69; 105,26</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31,82; 137,19</t>
+          <t>31,1; 132,56</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5,42; 72,83</t>
+          <t>4,03; 73,66</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,65; 70,85</t>
+          <t>1,67; 69,12</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>33,75; 105,76</t>
+          <t>30,89; 99,43</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,22; 77,51</t>
+          <t>16,86; 73,37</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>13,6; 68,34</t>
+          <t>11,85; 67,33</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>40,33; 96,85</t>
+          <t>39,41; 97,08</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>6,45</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,4</t>
+          <t>5,79</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8,05</t>
+          <t>6,12</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,85</t>
+          <t>2,04; 5,01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,04</t>
+          <t>2,19; 4,87</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,13</t>
+          <t>5,05; 7,9</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,15</t>
+          <t>1,79; 5,05</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,49</t>
+          <t>1,24; 4,53</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,26; 25,02</t>
+          <t>4,35; 7,32</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,56</t>
+          <t>2,4; 4,41</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,31</t>
+          <t>2,17; 4,32</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,09; 17,18</t>
+          <t>5,15; 7,19</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>100,95%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>21,72; 66,84</t>
+          <t>23,92; 68,49</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>25,63; 68,73</t>
+          <t>25,25; 67,66</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>33,69; 97,01</t>
+          <t>58,08; 108,56</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16,7; 54,43</t>
+          <t>16,46; 52,22</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>11,85; 46,84</t>
+          <t>11,17; 47,24</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>50,02; 252,33</t>
+          <t>39,41; 79,08</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,36; 52,46</t>
+          <t>24,84; 50,87</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>22,61; 50,27</t>
+          <t>22,37; 49,36</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>54,87; 186,31</t>
+          <t>53,01; 83,48</t>
         </is>
       </c>
     </row>
